--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0172.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0172.xlsx
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Gì? Cậu bảo cậu chỉ là cái rương bình thường, mà tên đó đã có người dùng rồi á?</t>
+          <t>Gì? Mày bảo mày chỉ là cái rương bình thường, mà tên đó đã có người dùng rồi á?</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>"{PlayerName}, cậu cứ lướt qua ta như gió, nhưng lại xa cách hơn cả mặt trăng."</t>
+          <t>"{PlayerName}, cậu cứ lướt qua tao như gió, nhưng lại xa cách hơn cả mặt trăng."</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} cầm lấy đi. Tôi không cần nữa rồi.</t>
+          <t>{Male=Mister;Female=Miss} cầm lấy đi. Tôi không cần nữa rồi.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Ta đã thử nhiều lần rồi, nhưng kết quả về bố lúc nào cũng tệ... Khi nào bố mới về nhà được nhỉ?</t>
+          <t>Tao đã thử nhiều lần rồi, nhưng kết quả về bố lúc nào cũng tệ... Khi nào bố mới về nhà được nhỉ?</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Những đoàn biểu diễn dưới lòng đất thật tuyệt vời... tiếc là ta không thể xem hết được...</t>
+          <t>Những đoàn biểu diễn dưới lòng đất thật tuyệt vời... tiếc là tao không thể xem hết được...</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Cậu đang bận gì thế?</t>
+          <t>Mày đang bận gì thế?</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Những đứa trẻ này vẫn còn quá nhỏ để hiểu rằng những Tiếng Vang này là phước lành từ Imperator.</t>
+          <t>Những đứa trẻ này vẫn còn quá nhỏ để hiểu rằng những Echo này là phước lành từ Imperator.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Không, ta nghĩ ngươi nên kiếm việc đi. Nếu không thì đi chăn cừu ở thị trấn cũng được. Ta quen người mà.</t>
+          <t>Không, tao nghĩ mày nên kiếm việc đi. Nếu không thì đi chăn cừu ở thị trấn cũng được. Tao quen người mà.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Nhưng ta vẫn tin là ngoài đời thật vẫn có những băng đảng như thế!</t>
+          <t>Nhưng tao vẫn tin là ngoài đời thật vẫn có những băng đảng như thế!</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Ừ. Nhưng cậu chưa thấy cái tệ nhất đâu. Có năm nước biển dâng lên ngập cả đường phố chính, gần ngập đến thắt lưng ta luôn.</t>
+          <t>Ừ. Nhưng cậu chưa thấy cái tệ nhất đâu. Có năm nước biển dâng lên ngập cả đường phố chính, gần ngập đến thắt lưng tao luôn.</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Ôi trời... Những lời cay nghiệt ấy. Bà ta ngụ ý là ta quá tầm thường so với gu của bà ta!</t>
+          <t>Ôi trời... Những lời cay nghiệt ấy. Bà ta ngụ ý là tao quá tầm thường so với gu của bà ta!</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Giờ ta mới nhớ lại cái thời Ngân hàng Averardo thu thập Monnaie để đổi tiền mới cho chúng ta.</t>
+          <t>Giờ tao mới nhớ lại cái thời Ngân hàng Averardo thu thập Monnaie để đổi tiền mới cho chúng ta.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Gọi ta là "Ngài" đi!</t>
+          <t>Gọi tao là "Ngài" đi!</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Đủ rồi! Ai thèm lấy tiền của cậu chứ!</t>
+          <t>Đủ rồi! Ai thèm lấy tiền của mày chứ!</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Cứ tiếp tục như thế, ta sẽ gọi Acolyte của Tòa Án Order đến đấy!</t>
+          <t>Cứ tiếp tục như thế, tao sẽ gọi Acolyte của Tòa Án Order đến đấy!</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Rồi thì, "Cả đời ta sống ở đây, chưa bao giờ thấy dân Ragunna nào say sóng cả!"</t>
+          <t>Rồi thì, "Cả đời tao sống ở đây, chưa bao giờ thấy dân Ragunna nào say sóng cả!"</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>...Cậu kia!</t>
+          <t>...Mày kia!</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Bọn ngươi đang cãi nhau gì thế? Ta nghe không rõ lắm.</t>
+          <t>Bọn mày đang cãi nhau gì thế? Tao nghe không rõ lắm.</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Có vẻ đây là lần đầu cậu thực hiện Nghi Lễ Cầu Triều. Ta đoán được ngay qua những động tác hơi vụng về và vẻ mặt đầy nghi hoặc của cậu.</t>
+          <t>Có vẻ đây là lần đầu cậu thực hiện Nghi Lễ Cầu Triều. Tao đoán được ngay qua những động tác hơi vụng về và vẻ mặt đầy nghi hoặc của cậu.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Xin lỗi, {Male=thưa ông;Female=thưa cô}! Tôi có thể thấy ông/cô là khách quý của Ragunna!</t>
+          <t>Xin lỗi, {Male=Sir;Female=Miss}! Tôi có thể thấy ông/cô là khách quý của Ragunna!</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Ngươi cần một thứ bùa may mắn—móng vuốt của kẻ trộm, Thief's Talon.</t>
+          <t>Mày cần một thứ bùa may mắn—móng vuốt của kẻ trộm, Thief's Talon.</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Đợi đã! {Male=Thưa ngài;Female=Thưa cô} đừng đi vội! Em còn nhiều món đồ khác nữa ạ! Nếu ngài thấy nhiều quá, em có thể giảm giá. Xin hãy xem qua một chút thôi...</t>
+          <t>Đợi đã! {Male=Sir;Female=Miss} đừng đi vội! Em còn nhiều món đồ khác nữa ạ! Nếu ngài thấy nhiều quá, em có thể giảm giá. Xin hãy xem qua một chút thôi...</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Hy vọng vậy. Miễn là Echo quý giá của ta trong kho không sao là được...</t>
+          <t>Hy vọng vậy. Miễn là Echo quý giá của tao trong kho không sao là được...</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Tiếng vọng quý giá? Tiếng vọng nào mà quý đến mức phải cất trong Kho Averardo chứ?</t>
+          <t>Echo quý giá? Echo nào mà quý đến mức phải cất trong Kho Averardo chứ?</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Ta cũng muốn giàu có! Ta muốn mọi người phải nể phục khi nghe đến tên ta! Ta sẽ tận dụng cơ hội này đến cùng!</t>
+          <t>Tao cũng muốn giàu có! Tao muốn mọi người phải nể phục khi nghe đến tên tao! Tao sẽ tận dụng cơ hội này đến cùng!</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Bạn đang nhìn gì vậy?</t>
+          <t>Nhìn gì thế?</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Chúc quý {Male=ông;Female=bà} một ngày tuyệt vời. Mong vận may luôn mỉm cười với ngài.</t>
+          <t>Chúc quý {Male=gentleman;Female=lady} một ngày tuyệt vời. Mong vận may luôn mỉm cười với ngài.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Ta vừa theo dõi vụ giao dịch nho nhỏ của cậu với {Male=quý ông;Female=quý bà} này đấy.</t>
+          <t>Ta vừa theo dõi vụ giao dịch nho nhỏ của cậu với {Male=gentleman;Female=lady} này đấy.</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Suỵt—đừng có phá suy nghĩ của ta!</t>
+          <t>Suỵt—đừng có phá suy nghĩ của tao!</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Không đời nào, {Male=ông này;Female=bà này} trông khỏe thế đủ đánh bại tớ dễ dàng luôn.</t>
+          <t>Không đời nào, {Male=gentleman;Female=lady} trông khỏe thế đủ đánh bại tớ dễ dàng luôn.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Ừm... {Male=anh ấy;Female=cô ấy} đẹp trai thế này, chắc mấy họa sĩ ở Ragunna tranh nhau vẽ {Male=anh ấy;Female=cô ấy} mất thôi.</t>
+          <t>Ừm... {Male=him;Female=her} đẹp trai thế này, chắc mấy họa sĩ ở Ragunna tranh nhau vẽ {Male=him;Female=her} mất thôi.</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Ngươi thấy ta nghèo à?</t>
+          <t>Mày thấy tao nghèo à?</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Vậy, cậu định trả lại khách hàng gấp mười lần hay đi với ta, Paolo?</t>
+          <t>Vậy, cậu định trả lại khách hàng gấp mười lần hay đi với tao, Paolo?</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Ngươi nợ ta 30.000 Shell Credits!</t>
+          <t>Mày nợ tao 30.000 Shell Credits!</t>
         </is>
       </c>
     </row>
